--- a/output/pdf_financials_xlsx/NVX.xlsx
+++ b/output/pdf_financials_xlsx/NVX.xlsx
@@ -5998,49 +5998,49 @@
         <v>0.276998</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.314517</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.462759</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.462759</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.622942</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.031185</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.031185</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.818573</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.052956</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.400151</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.73389</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.487649</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.655935</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.785373</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.894956</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.991322</v>
       </c>
     </row>
     <row r="93">
@@ -9560,7 +9560,11 @@
           <t>Share-based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -11068,7 +11072,11 @@
           <t>Share-based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NVX.xlsx
+++ b/output/pdf_financials_xlsx/NVX.xlsx
@@ -1032,52 +1032,52 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001648</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005439</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003962</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000725</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000135</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>5.5e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>5.3e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003908</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.007521</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.013329</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.007826</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00656</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.007077</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.012195</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000481</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000972</v>
       </c>
     </row>
     <row r="13">
@@ -1976,52 +1976,52 @@
         <v>-0.035686</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.000494</v>
+        <v>-1.002142</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.85456</v>
+        <v>-0.859999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.971023</v>
+        <v>-0.974985</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.504683</v>
+        <v>-0.505408</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.410643</v>
+        <v>-0.410778</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.412086</v>
+        <v>-3.412141</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.04636</v>
+        <v>-0.046413</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.85204</v>
+        <v>-1.855948</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.733048</v>
+        <v>-0.740569</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.675539</v>
+        <v>-3.688868</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.21334</v>
+        <v>-1.221166</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.545108</v>
+        <v>-5.551668</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.25132</v>
+        <v>-1.258397</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.741109</v>
+        <v>-2.753304</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.584421</v>
+        <v>-0.584902</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.419634</v>
+        <v>-1.420606</v>
       </c>
     </row>
     <row r="28">
@@ -2092,52 +2092,52 @@
         <v>-0.035686</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.000494</v>
+        <v>-1.002142</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.85456</v>
+        <v>-0.859999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.971023</v>
+        <v>-0.974985</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.504683</v>
+        <v>-0.505408</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.410643</v>
+        <v>-0.410778</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.412086</v>
+        <v>-3.412141</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.04636</v>
+        <v>-0.046413</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.85204</v>
+        <v>-1.855948</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.733048</v>
+        <v>-0.740569</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.675539</v>
+        <v>-3.688868</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.21334</v>
+        <v>-1.221166</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.545108</v>
+        <v>-5.551668</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.25132</v>
+        <v>-1.258397</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.741109</v>
+        <v>-2.753304</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.584421</v>
+        <v>-0.584902</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.419634</v>
+        <v>-1.420606</v>
       </c>
     </row>
     <row r="30">
@@ -2396,55 +2396,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.091048</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.655573</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.939896</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.123136</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.072697</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.470016</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.028695</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.328198</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.506132</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.404251</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.955877</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.333613</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.506257</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.291948</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.056814</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.031204</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.041157</v>
       </c>
     </row>
     <row r="35">
@@ -2512,55 +2512,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.091048</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.655573</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.939896</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.123136</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.072697</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.470016</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.028695</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.328198</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.506132</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.404251</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.955877</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.333613</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.506257</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.291948</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.056814</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.031204</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.041157</v>
       </c>
     </row>
     <row r="37">
@@ -3208,55 +3208,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.091048</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.657962</v>
+        <v>0.002389</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.948121</v>
+        <v>0.008225</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.123136</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.072697</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.498636</v>
+        <v>0.02862</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.029788</v>
+        <v>0.001093</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.329266</v>
+        <v>0.001068</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.533922</v>
+        <v>0.02779</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.41587</v>
+        <v>0.011619</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.048575</v>
+        <v>0.092698</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.408032</v>
+        <v>0.074419</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.780671</v>
+        <v>0.274414</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.357418</v>
+        <v>0.06547</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.200389</v>
+        <v>0.143575</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.035409</v>
+        <v>0.004205</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.047663</v>
+        <v>0.006506</v>
       </c>
     </row>
     <row r="49">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -18283,7 +18283,11 @@
           <t>Write-off of reclamation deposit</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -22246,7 +22250,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -25718,7 +25722,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">

--- a/output/pdf_financials_xlsx/NVX.xlsx
+++ b/output/pdf_financials_xlsx/NVX.xlsx
@@ -4241,52 +4241,52 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.017921</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.105136</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.007903</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.020121</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.157624</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.001217</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.012039</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.185461</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.071647</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.058628</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.061626</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.102108</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.01819</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.005062</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.012865</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.08655500000000001</v>
       </c>
     </row>
     <row r="65">
